--- a/backend/storage/imports/Master_SBM/6. SATUAN BIAYA BANTUAN BEASISWA PROGRAM GELARNONGELAR DALAM NEGERI.xlsx
+++ b/backend/storage/imports/Master_SBM/6. SATUAN BIAYA BANTUAN BEASISWA PROGRAM GELARNONGELAR DALAM NEGERI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE71026-E14E-4ED9-8728-903AFF6F99C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30A6C86-FD74-4E6F-A87F-7B9E3DC61800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5B2B8CBD-B645-41E8-B80F-F6263C0E3137}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t>NO</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Strata  3  dan  Spesialis  2</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>SATUAN BIAYA BANTUAN BEASISWA PROGRAM GELAR/NONGELAR DALAM NEGERI</t>
@@ -103,7 +100,7 @@
     <numFmt numFmtId="166" formatCode="[$Rp-421]#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,13 +121,6 @@
     </font>
     <font>
       <sz val="8.5"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
       <color rgb="FF000000"/>
       <name val="Calibri Light"/>
       <family val="1"/>
@@ -145,7 +135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -168,11 +158,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -180,22 +201,34 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3ABD124-C955-4CC4-B2FD-5244D9A833A2}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.77734375" customWidth="1"/>
@@ -520,143 +553,169 @@
     <col min="4" max="4" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="6">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>-1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B4" s="2">
         <v>-2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C4" s="2">
         <v>-3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D4" s="2">
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="5" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>27600000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>6.1</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="5">
-        <v>27600000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>6.2</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B8" s="2">
+        <v>-2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1662500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1987500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2312500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="5">
-        <v>2650000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="4">
+        <v>1662500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
+        <v>1987500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2312500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2650000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4">
         <v>2975000</v>
       </c>
     </row>
